--- a/Tech28/Lecture/NỘI DUNG BUỔI HỌC..xlsx
+++ b/Tech28/Lecture/NỘI DUNG BUỔI HỌC..xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RHNA\Visual\_Data structure\_DSA_RHNA\Tech28\Lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C41284-62EE-466D-998E-6AB6B896F02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A4D7D2-4134-417A-9DB9-AF09DD5E5451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="123">
   <si>
     <t>Ngày</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>Đồ thị Hai phía</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5mfgKnwXAwI&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=17</t>
   </si>
 </sst>
 </file>
@@ -812,7 +815,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -891,13 +894,7 @@
     <xf numFmtId="14" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -942,6 +939,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -963,25 +969,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1008,40 +1017,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1056,34 +1062,13 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1098,14 +1083,38 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1329,8 +1338,8 @@
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.1328125" style="38" customWidth="1"/>
-    <col min="2" max="2" width="13.3984375" style="38" customWidth="1"/>
+    <col min="1" max="1" width="8.1328125" style="36" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" style="36" customWidth="1"/>
     <col min="3" max="3" width="64.59765625" style="28" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="74.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.1328125" style="28" bestFit="1" customWidth="1"/>
@@ -1338,7 +1347,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39"/>
+      <c r="A1" s="37"/>
       <c r="B1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1353,10 +1362,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="47">
+      <c r="A2" s="48">
         <v>1</v>
       </c>
-      <c r="B2" s="50">
+      <c r="B2" s="51">
         <v>45012</v>
       </c>
       <c r="C2" s="25" t="s">
@@ -1370,8 +1379,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="48"/>
-      <c r="B3" s="51"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="25" t="s">
         <v>7</v>
       </c>
@@ -1381,8 +1390,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="48"/>
-      <c r="B4" s="51"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="25" t="s">
         <v>9</v>
       </c>
@@ -1390,8 +1399,8 @@
       <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="49"/>
-      <c r="B5" s="52"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="25" t="s">
         <v>10</v>
       </c>
@@ -1399,10 +1408,10 @@
       <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="53">
+      <c r="A6" s="54">
         <v>2</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="61">
         <v>45015</v>
       </c>
       <c r="C6" s="24" t="s">
@@ -1411,35 +1420,35 @@
       <c r="D6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="75" t="s">
+      <c r="E6" s="45" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="54"/>
-      <c r="B7" s="57"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="75"/>
       <c r="C7" s="24" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="76"/>
+      <c r="E7" s="46"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="55"/>
-      <c r="B8" s="58"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="24"/>
       <c r="D8" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="77"/>
+      <c r="E8" s="47"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="47">
+      <c r="A9" s="48">
         <v>3</v>
       </c>
-      <c r="B9" s="50">
+      <c r="B9" s="51">
         <v>45019</v>
       </c>
       <c r="C9" s="25" t="s">
@@ -1451,8 +1460,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="48"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="25" t="s">
         <v>19</v>
       </c>
@@ -1460,8 +1469,8 @@
       <c r="E10" s="25"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="48"/>
-      <c r="B11" s="51"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="52"/>
       <c r="C11" s="25" t="s">
         <v>20</v>
       </c>
@@ -1469,8 +1478,8 @@
       <c r="E11" s="25"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="49"/>
-      <c r="B12" s="52"/>
+      <c r="A12" s="50"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="25" t="s">
         <v>21</v>
       </c>
@@ -1478,7 +1487,7 @@
       <c r="E12" s="25"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="40">
+      <c r="A13" s="38">
         <v>4</v>
       </c>
       <c r="B13" s="29">
@@ -1493,10 +1502,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="47">
+      <c r="A14" s="48">
         <v>5</v>
       </c>
-      <c r="B14" s="59">
+      <c r="B14" s="56">
         <v>45026</v>
       </c>
       <c r="C14" s="25" t="s">
@@ -1508,8 +1517,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="48"/>
-      <c r="B15" s="78"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="25" t="s">
         <v>26</v>
       </c>
@@ -1517,8 +1526,8 @@
       <c r="E15" s="25"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="48"/>
-      <c r="B16" s="78"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="25" t="s">
         <v>27</v>
       </c>
@@ -1526,8 +1535,8 @@
       <c r="E16" s="25"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="48"/>
-      <c r="B17" s="78"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="25" t="s">
         <v>28</v>
       </c>
@@ -1535,8 +1544,8 @@
       <c r="E17" s="25"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="48"/>
-      <c r="B18" s="78"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="25" t="s">
         <v>29</v>
       </c>
@@ -1544,8 +1553,8 @@
       <c r="E18" s="25"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="49"/>
-      <c r="B19" s="60"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="25" t="s">
         <v>30</v>
       </c>
@@ -1553,10 +1562,10 @@
       <c r="E19" s="25"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="53">
+      <c r="A20" s="54">
         <v>6</v>
       </c>
-      <c r="B20" s="69">
+      <c r="B20" s="59">
         <v>45029</v>
       </c>
       <c r="C20" s="24" t="s">
@@ -1569,7 +1578,7 @@
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="55"/>
-      <c r="B21" s="70"/>
+      <c r="B21" s="60"/>
       <c r="C21" s="24" t="s">
         <v>33</v>
       </c>
@@ -1577,10 +1586,10 @@
       <c r="E21" s="24"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="47">
+      <c r="A22" s="48">
         <v>7</v>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="51">
         <v>45033</v>
       </c>
       <c r="C22" s="25" t="s">
@@ -1594,8 +1603,8 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="48"/>
-      <c r="B23" s="51"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="25" t="s">
         <v>37</v>
       </c>
@@ -1605,8 +1614,8 @@
       <c r="E23" s="25"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="48"/>
-      <c r="B24" s="51"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="52"/>
       <c r="C24" s="25" t="s">
         <v>39</v>
       </c>
@@ -1616,8 +1625,8 @@
       <c r="E24" s="25"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="25" t="s">
         <v>41</v>
       </c>
@@ -1625,10 +1634,10 @@
       <c r="E25" s="25"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="53">
+      <c r="A26" s="54">
         <v>8</v>
       </c>
-      <c r="B26" s="56">
+      <c r="B26" s="61">
         <v>45036</v>
       </c>
       <c r="C26" s="24" t="s">
@@ -1641,7 +1650,7 @@
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="55"/>
-      <c r="B27" s="58"/>
+      <c r="B27" s="62"/>
       <c r="C27" s="24" t="s">
         <v>44</v>
       </c>
@@ -1649,10 +1658,10 @@
       <c r="E27" s="24"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="47">
+      <c r="A28" s="48">
         <v>9</v>
       </c>
-      <c r="B28" s="50">
+      <c r="B28" s="51">
         <v>45040</v>
       </c>
       <c r="C28" s="25" t="s">
@@ -1662,8 +1671,8 @@
       <c r="E28" s="25"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="49"/>
-      <c r="B29" s="52"/>
+      <c r="A29" s="50"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="25" t="s">
         <v>46</v>
       </c>
@@ -1671,10 +1680,10 @@
       <c r="E29" s="25"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="40">
+      <c r="A30" s="38">
         <v>10</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>45043</v>
       </c>
       <c r="C30" s="24" t="s">
@@ -1686,8 +1695,8 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="40"/>
-      <c r="B31" s="31"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="24" t="s">
         <v>49</v>
       </c>
@@ -1695,10 +1704,10 @@
       <c r="E31" s="24"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="47">
+      <c r="A32" s="48">
         <v>11</v>
       </c>
-      <c r="B32" s="59">
+      <c r="B32" s="51">
         <v>45050</v>
       </c>
       <c r="C32" s="25" t="s">
@@ -1710,8 +1719,8 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="49"/>
-      <c r="B33" s="60"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="53"/>
       <c r="C33" s="25" t="s">
         <v>52</v>
       </c>
@@ -1719,10 +1728,10 @@
       <c r="E33" s="25"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="53">
+      <c r="A34" s="54">
         <v>12</v>
       </c>
-      <c r="B34" s="69">
+      <c r="B34" s="61">
         <v>45054</v>
       </c>
       <c r="C34" s="24" t="s">
@@ -1735,7 +1744,7 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="55"/>
-      <c r="B35" s="70"/>
+      <c r="B35" s="62"/>
       <c r="C35" s="24" t="s">
         <v>55</v>
       </c>
@@ -1743,13 +1752,13 @@
       <c r="E35" s="24"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="47">
+      <c r="A36" s="48">
         <v>13</v>
       </c>
-      <c r="B36" s="59">
+      <c r="B36" s="56">
         <v>45057</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="99" t="s">
         <v>56</v>
       </c>
       <c r="D36" s="25"/>
@@ -1758,9 +1767,9 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="49"/>
-      <c r="B37" s="60"/>
-      <c r="C37" s="25" t="s">
+      <c r="A37" s="50"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="99" t="s">
         <v>58</v>
       </c>
       <c r="D37" s="25"/>
@@ -1769,10 +1778,10 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="47">
+      <c r="A38" s="48">
         <v>14</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="103">
         <v>45064</v>
       </c>
       <c r="C38" s="25" t="s">
@@ -1782,8 +1791,8 @@
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="49"/>
-      <c r="B39" s="33"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="25" t="s">
         <v>61</v>
       </c>
@@ -1791,20 +1800,22 @@
       <c r="E39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="67">
+      <c r="A40" s="69">
         <v>15</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="46" t="s">
+      <c r="B40" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C40" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="71"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="43" t="s">
+      <c r="B41" s="101"/>
+      <c r="C41" s="41" t="s">
         <v>63</v>
       </c>
       <c r="D41" s="27"/>
@@ -1812,8 +1823,8 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="71"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="43" t="s">
+      <c r="B42" s="101"/>
+      <c r="C42" s="41" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="27"/>
@@ -1821,8 +1832,8 @@
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="71"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="43" t="s">
+      <c r="B43" s="101"/>
+      <c r="C43" s="41" t="s">
         <v>65</v>
       </c>
       <c r="D43" s="27"/>
@@ -1830,142 +1841,142 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="71"/>
-      <c r="B44" s="73"/>
-      <c r="C44" s="43" t="s">
+      <c r="B44" s="101"/>
+      <c r="C44" s="41" t="s">
         <v>69</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="27"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="68"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="43" t="s">
+      <c r="A45" s="70"/>
+      <c r="B45" s="102"/>
+      <c r="C45" s="41" t="s">
         <v>66</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="27"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="61">
+      <c r="A46" s="63">
         <v>16</v>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="32">
         <v>45071</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="40" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="26"/>
-      <c r="E46" s="42" t="s">
+      <c r="E46" s="40" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="63"/>
-      <c r="B47" s="35"/>
-      <c r="C47" s="42" t="s">
+      <c r="A47" s="65"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="40" t="s">
         <v>68</v>
       </c>
       <c r="D47" s="26"/>
       <c r="E47" s="26"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="67">
+      <c r="A48" s="69">
         <v>17</v>
       </c>
       <c r="B48" s="72"/>
-      <c r="C48" s="43" t="s">
+      <c r="C48" s="41" t="s">
         <v>71</v>
       </c>
       <c r="D48" s="27"/>
-      <c r="E48" s="43" t="s">
+      <c r="E48" s="41" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="68"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="43" t="s">
+      <c r="A49" s="70"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="41" t="s">
         <v>73</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="27"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="61">
+      <c r="A50" s="63">
         <v>18</v>
       </c>
-      <c r="B50" s="64">
+      <c r="B50" s="66">
         <v>45078</v>
       </c>
-      <c r="C50" s="44" t="s">
+      <c r="C50" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="D50" s="45"/>
-      <c r="E50" s="44" t="s">
+      <c r="D50" s="43"/>
+      <c r="E50" s="42" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="62"/>
-      <c r="B51" s="65"/>
-      <c r="C51" s="42" t="s">
+      <c r="A51" s="64"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="40" t="s">
         <v>75</v>
       </c>
       <c r="D51" s="26"/>
       <c r="E51" s="26"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="62"/>
-      <c r="B52" s="65"/>
-      <c r="C52" s="42" t="s">
+      <c r="A52" s="64"/>
+      <c r="B52" s="67"/>
+      <c r="C52" s="40" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="26"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="63"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="42" t="s">
+      <c r="A53" s="65"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="40" t="s">
         <v>77</v>
       </c>
       <c r="D53" s="26"/>
       <c r="E53" s="26"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="67">
+      <c r="A54" s="69">
         <v>19</v>
       </c>
-      <c r="B54" s="36">
+      <c r="B54" s="34">
         <v>45082</v>
       </c>
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="41" t="s">
         <v>78</v>
       </c>
       <c r="D54" s="27"/>
-      <c r="E54" s="43" t="s">
+      <c r="E54" s="41" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="68"/>
-      <c r="B55" s="37"/>
-      <c r="C55" s="43" t="s">
+      <c r="A55" s="70"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D55" s="27"/>
       <c r="E55" s="27"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="61">
+      <c r="A56" s="63">
         <v>20</v>
       </c>
-      <c r="B56" s="34">
+      <c r="B56" s="32">
         <v>45085</v>
       </c>
-      <c r="C56" s="42" t="s">
+      <c r="C56" s="40" t="s">
         <v>80</v>
       </c>
       <c r="D56" s="26"/>
@@ -1974,9 +1985,9 @@
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="63"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="42" t="s">
+      <c r="A57" s="65"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="40" t="s">
         <v>82</v>
       </c>
       <c r="D57" s="26"/>
@@ -2927,18 +2938,13 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B28:B29"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="A54:A55"/>
@@ -2953,13 +2959,18 @@
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B2:B5" r:id="rId1" display="https://www.youtube.com/watch?v=3FbI-Qs17xs&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp" xr:uid="{7CF903A2-1C55-4B9E-A7CE-622C8EE471E4}"/>
@@ -2969,9 +2980,16 @@
     <hyperlink ref="B22:B25" r:id="rId5" display="https://www.youtube.com/watch?v=XhyxVGuOpw8&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=7" xr:uid="{49B14657-9ACB-4548-B8BF-F87B3EA28C27}"/>
     <hyperlink ref="B26:B27" r:id="rId6" display="https://www.youtube.com/watch?v=zZIJEYwEcmQ&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=8" xr:uid="{9281A718-1A99-41D1-80A7-BFC4DB69F921}"/>
     <hyperlink ref="B28:B29" r:id="rId7" display="https://www.youtube.com/watch?v=ZuFRcZFNMqQ" xr:uid="{A04BED43-C17E-45F0-98C8-62AB9B24196F}"/>
+    <hyperlink ref="B30" r:id="rId8" display="https://www.youtube.com/watch?v=pkWSjOiS_Zk&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=11" xr:uid="{AF3F2779-0521-498B-997C-FA0CBBB37669}"/>
+    <hyperlink ref="B32:B33" r:id="rId9" display="https://www.youtube.com/watch?v=paWWB3F5Fwk&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=12" xr:uid="{5E981926-76E8-4A0A-867D-2662CAB9DF83}"/>
+    <hyperlink ref="B34:B35" r:id="rId10" display="https://www.youtube.com/watch?v=1IvGgM-xe1w&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=13" xr:uid="{C8CBFF67-EED9-4024-BDCA-8F8EAE8CF9CB}"/>
+    <hyperlink ref="C36" r:id="rId11" xr:uid="{0828C755-7A8F-46C7-A61E-4BAED3AB2FF9}"/>
+    <hyperlink ref="C37" r:id="rId12" xr:uid="{53FC6723-3686-4076-8B1F-D2E43D24711E}"/>
+    <hyperlink ref="B40:B45" r:id="rId13" display="https://www.youtube.com/watch?v=5mfgKnwXAwI&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=17" xr:uid="{F7C3B268-F8F7-47F1-8BEE-7B71D1777077}"/>
+    <hyperlink ref="B38" r:id="rId14" display="https://www.youtube.com/watch?v=5mfgKnwXAwI&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=17" xr:uid="{A8A9302E-4D50-4ADC-AB01-044E68C6D127}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -3058,13 +3076,13 @@
       <c r="Y2" s="10"/>
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="79">
+      <c r="A3" s="86">
         <v>2</v>
       </c>
-      <c r="B3" s="81">
+      <c r="B3" s="82">
         <v>2</v>
       </c>
-      <c r="C3" s="83">
+      <c r="C3" s="84">
         <v>45017</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -3093,9 +3111,9 @@
       <c r="Y3" s="12"/>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="80"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="84"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="85"/>
       <c r="D4" s="11" t="s">
         <v>88</v>
       </c>
@@ -3122,13 +3140,13 @@
       <c r="Y4" s="12"/>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="85">
+      <c r="A5" s="93">
         <v>3</v>
       </c>
-      <c r="B5" s="88">
+      <c r="B5" s="76">
         <v>3</v>
       </c>
-      <c r="C5" s="91">
+      <c r="C5" s="96">
         <v>45021</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -3157,9 +3175,9 @@
       <c r="Y5" s="12"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="86"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="92"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="97"/>
       <c r="D6" s="9" t="s">
         <v>90</v>
       </c>
@@ -3186,9 +3204,9 @@
       <c r="Y6" s="12"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="87"/>
-      <c r="B7" s="90"/>
-      <c r="C7" s="93"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="9" t="s">
         <v>91</v>
       </c>
@@ -3215,13 +3233,13 @@
       <c r="Y7" s="12"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="79">
+      <c r="A8" s="86">
         <v>4</v>
       </c>
-      <c r="B8" s="81">
+      <c r="B8" s="82">
         <v>4</v>
       </c>
-      <c r="C8" s="96">
+      <c r="C8" s="90">
         <v>45024</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -3250,9 +3268,9 @@
       <c r="Y8" s="12"/>
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="94"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="97"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="91"/>
       <c r="D9" s="11" t="s">
         <v>93</v>
       </c>
@@ -3279,9 +3297,9 @@
       <c r="Y9" s="10"/>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="80"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="98"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="11" t="s">
         <v>94</v>
       </c>
@@ -3308,13 +3326,13 @@
       <c r="Y10" s="10"/>
     </row>
     <row r="11" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="88">
+      <c r="A11" s="76">
         <v>5</v>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="76">
         <v>5</v>
       </c>
-      <c r="C11" s="99">
+      <c r="C11" s="79">
         <v>45028</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -3343,9 +3361,9 @@
       <c r="Y11" s="10"/>
     </row>
     <row r="12" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="90"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="100"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="81"/>
       <c r="D12" s="9" t="s">
         <v>96</v>
       </c>
@@ -3407,13 +3425,13 @@
       <c r="Y13" s="10"/>
     </row>
     <row r="14" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="88">
+      <c r="A14" s="76">
         <v>7</v>
       </c>
-      <c r="B14" s="88">
+      <c r="B14" s="76">
         <v>7</v>
       </c>
-      <c r="C14" s="99">
+      <c r="C14" s="79">
         <v>45035</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -3442,9 +3460,9 @@
       <c r="Y14" s="10"/>
     </row>
     <row r="15" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="89"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="101"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="80"/>
       <c r="D15" s="9" t="s">
         <v>99</v>
       </c>
@@ -3471,9 +3489,9 @@
       <c r="Y15" s="10"/>
     </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="90"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="100"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="81"/>
       <c r="D16" s="9" t="s">
         <v>100</v>
       </c>
@@ -3500,13 +3518,13 @@
       <c r="Y16" s="10"/>
     </row>
     <row r="17" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="81">
+      <c r="A17" s="82">
         <v>8</v>
       </c>
-      <c r="B17" s="81">
+      <c r="B17" s="82">
         <v>8</v>
       </c>
-      <c r="C17" s="83">
+      <c r="C17" s="84">
         <v>45039</v>
       </c>
       <c r="D17" s="11" t="s">
@@ -3535,9 +3553,9 @@
       <c r="Y17" s="10"/>
     </row>
     <row r="18" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="82"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="84"/>
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="11" t="s">
         <v>102</v>
       </c>
@@ -3669,13 +3687,13 @@
       <c r="Y21" s="10"/>
     </row>
     <row r="22" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="81">
+      <c r="A22" s="82">
         <v>12</v>
       </c>
-      <c r="B22" s="81">
+      <c r="B22" s="82">
         <v>12</v>
       </c>
-      <c r="C22" s="83">
+      <c r="C22" s="84">
         <v>45059</v>
       </c>
       <c r="D22" s="11" t="s">
@@ -3704,9 +3722,9 @@
       <c r="Y22" s="10"/>
     </row>
     <row r="23" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="82"/>
-      <c r="B23" s="82"/>
-      <c r="C23" s="84"/>
+      <c r="A23" s="83"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="11" t="s">
         <v>107</v>
       </c>
@@ -3803,13 +3821,13 @@
       <c r="Y25" s="10"/>
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="88">
+      <c r="A26" s="76">
         <v>15</v>
       </c>
-      <c r="B26" s="88">
+      <c r="B26" s="76">
         <v>15</v>
       </c>
-      <c r="C26" s="99">
+      <c r="C26" s="79">
         <v>45070</v>
       </c>
       <c r="D26" s="9" t="s">
@@ -3838,9 +3856,9 @@
       <c r="Y26" s="10"/>
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="89"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="101"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="80"/>
       <c r="D27" s="9" t="s">
         <v>111</v>
       </c>
@@ -3867,9 +3885,9 @@
       <c r="Y27" s="10"/>
     </row>
     <row r="28" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="90"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="100"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="81"/>
       <c r="D28" s="9" t="s">
         <v>112</v>
       </c>
@@ -3931,13 +3949,13 @@
       <c r="Y29" s="10"/>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="88">
+      <c r="A30" s="76">
         <v>17</v>
       </c>
-      <c r="B30" s="88">
+      <c r="B30" s="76">
         <v>17</v>
       </c>
-      <c r="C30" s="99">
+      <c r="C30" s="79">
         <v>45077</v>
       </c>
       <c r="D30" s="16" t="s">
@@ -3966,9 +3984,9 @@
       <c r="Y30" s="10"/>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="89"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="101"/>
+      <c r="A31" s="77"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="80"/>
       <c r="D31" s="9" t="s">
         <v>115</v>
       </c>
@@ -3995,9 +4013,9 @@
       <c r="Y31" s="10"/>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="90"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="100"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="9" t="s">
         <v>116</v>
       </c>
@@ -4024,13 +4042,13 @@
       <c r="Y32" s="10"/>
     </row>
     <row r="33" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="81">
+      <c r="A33" s="82">
         <v>18</v>
       </c>
-      <c r="B33" s="81">
+      <c r="B33" s="82">
         <v>18</v>
       </c>
-      <c r="C33" s="83">
+      <c r="C33" s="84">
         <v>45080</v>
       </c>
       <c r="D33" s="19" t="s">
@@ -4059,9 +4077,9 @@
       <c r="Y33" s="10"/>
     </row>
     <row r="34" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="82"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="84"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="85"/>
       <c r="D34" s="11" t="s">
         <v>118</v>
       </c>
@@ -4088,13 +4106,13 @@
       <c r="Y34" s="10"/>
     </row>
     <row r="35" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="88">
+      <c r="A35" s="76">
         <v>19</v>
       </c>
-      <c r="B35" s="88">
+      <c r="B35" s="76">
         <v>19</v>
       </c>
-      <c r="C35" s="99">
+      <c r="C35" s="79">
         <v>45084</v>
       </c>
       <c r="D35" s="16" t="s">
@@ -4123,9 +4141,9 @@
       <c r="Y35" s="10"/>
     </row>
     <row r="36" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="89"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="101"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="80"/>
       <c r="D36" s="9" t="s">
         <v>120</v>
       </c>
@@ -4152,9 +4170,9 @@
       <c r="Y36" s="10"/>
     </row>
     <row r="37" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="90"/>
-      <c r="B37" s="90"/>
-      <c r="C37" s="100"/>
+      <c r="A37" s="78"/>
+      <c r="B37" s="78"/>
+      <c r="C37" s="81"/>
       <c r="D37" s="9" t="s">
         <v>121</v>
       </c>
@@ -9903,6 +9921,30 @@
     <row r="1000" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C26:C28"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="B35:B37"/>
     <mergeCell ref="C35:C37"/>
@@ -9912,30 +9954,6 @@
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="C33:C34"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5:C7" r:id="rId1" display="https://www.youtube.com/watch?v=bPYoOeMVj_g&amp;list=PLV7ZogLwWKR_qiot9r4_ERAEJlrbVbPxp&amp;index=4" xr:uid="{F6ACBA35-8ACF-4640-9A67-081896D5D73F}"/>
